--- a/results/link-prediction-gcn/Link/5shot/MUTAG/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/MUTAG/GCN_total_results.xlsx
@@ -898,62 +898,62 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.7104±0.0131</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6276±0.0536</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.6661±0.0000</t>
+          <t>0.6647±0.0010</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6778±0.0382</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.6691±0.0000</t>
+          <t>0.7269±0.0049</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.6691±0.0000</t>
+          <t>0.6835±0.0103</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.7275±0.0119</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.7275±0.0119</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.7275±0.0119</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.7058±0.0332</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.7196±0.0000</t>
+          <t>0.6670±0.0462</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.7311±0.0090</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -963,62 +963,62 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.6661±0.0000</t>
+          <t>0.6611±0.0054</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6366±0.0248</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.6959±0.0000</t>
+          <t>0.6885±0.0252</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6970±0.0198</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6613±0.0030</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6617±0.0032</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.6665±0.0058</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.6665±0.0058</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.6665±0.0058</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6629±0.0016</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6750±0.0000</t>
+          <t>0.6384±0.0304</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6819±0.0183</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1028,62 +1028,62 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5161±0.0000</t>
+          <t>0.6558±0.0950</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.6536±0.0000</t>
+          <t>0.6087±0.0372</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.4955±0.0000</t>
+          <t>0.6692±0.0549</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.6357±0.0000</t>
+          <t>0.6911±0.0599</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5250±0.0000</t>
+          <t>0.5952±0.0893</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.4937±0.0000</t>
+          <t>0.7360±0.0239</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5866±0.1017</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5866±0.1017</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5188±0.0000</t>
+          <t>0.5866±0.1017</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5286±0.0000</t>
+          <t>0.7356±0.0247</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5768±0.0000</t>
+          <t>0.5194±0.0116</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5607±0.0000</t>
+          <t>0.6107±0.0569</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1093,62 +1093,62 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.7138±0.0000</t>
+          <t>0.6492±0.0179</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.6154±0.0000</t>
+          <t>0.6927±0.0317</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.6869±0.0000</t>
+          <t>0.6446±0.0064</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7238±0.0045</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.6834±0.0000</t>
+          <t>0.7030±0.0299</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.6744±0.0000</t>
+          <t>0.6510±0.0166</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.7048±0.0000</t>
+          <t>0.6969±0.0097</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.7048±0.0000</t>
+          <t>0.6969±0.0097</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.7048±0.0000</t>
+          <t>0.6969±0.0097</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.6959±0.0000</t>
+          <t>0.6931±0.0189</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.6512±0.0000</t>
+          <t>0.6472±0.0059</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.7102±0.0000</t>
+          <t>0.7088±0.0115</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1158,62 +1158,62 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.6852±0.0000</t>
+          <t>0.6766±0.0217</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.6422±0.0000</t>
+          <t>0.6167±0.0170</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.6297±0.0000</t>
+          <t>0.6268±0.0162</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6555±0.0078</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.6744±0.0000</t>
+          <t>0.6854±0.0166</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.6786±0.0000</t>
+          <t>0.6988±0.0300</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6855±0.0180</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6855±0.0180</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6855±0.0180</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.6821±0.0000</t>
+          <t>0.6824±0.0268</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.6713±0.0324</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.6732±0.0000</t>
+          <t>0.6814±0.0094</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1223,62 +1223,62 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.7066±0.0000</t>
+          <t>0.7016±0.0039</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.6637±0.0000</t>
+          <t>0.6097±0.0185</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.6286±0.0000</t>
+          <t>0.6296±0.0235</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.6601±0.0000</t>
+          <t>0.6579±0.0263</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6849±0.0183</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.6946±0.0000</t>
+          <t>0.6536±0.0144</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.6982±0.0000</t>
+          <t>0.6498±0.0062</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.6982±0.0000</t>
+          <t>0.6498±0.0062</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.6982±0.0000</t>
+          <t>0.6498±0.0062</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.6911±0.0000</t>
+          <t>0.6794±0.0104</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.7138±0.0000</t>
+          <t>0.6486±0.0153</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6643±0.0336</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1288,62 +1288,62 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.6869±0.0000</t>
+          <t>0.6478±0.0151</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.6583±0.0000</t>
+          <t>0.6915±0.0295</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.6118±0.0000</t>
+          <t>0.6375±0.0130</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.6601±0.0000</t>
+          <t>0.7030±0.0295</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.6429±0.0000</t>
+          <t>0.6450±0.0172</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6905±0.0000</t>
+          <t>0.6605±0.0233</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.6625±0.0266</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.6764±0.0217</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.6764±0.0217</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6796±0.0216</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6071±0.0000</t>
+          <t>0.6466±0.0058</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.6887±0.0000</t>
+          <t>0.6611±0.0313</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.8017±0.0000</t>
+          <t>0.8004±0.0075</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7559±0.0612</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7976±0.0002</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7773±0.0349</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.8009±0.0000</t>
+          <t>0.8137±0.0032</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7996±0.0000</t>
+          <t>0.7770±0.0134</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.8017±0.0000</t>
+          <t>0.8139±0.0063</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8017±0.0000</t>
+          <t>0.8139±0.0063</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.8017±0.0000</t>
+          <t>0.8139±0.0063</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7944±0.0271</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8055±0.0000</t>
+          <t>0.7569±0.0432</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.8017±0.0000</t>
+          <t>0.8157±0.0053</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7958±0.0041</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7568±0.0416</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.8073±0.0000</t>
+          <t>0.7990±0.0148</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7983±0.0076</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7961±0.0022</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7837±0.0171</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8000±0.0000</t>
+          <t>0.7977±0.0015</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.8000±0.0000</t>
+          <t>0.7977±0.0015</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.8000±0.0000</t>
+          <t>0.7977±0.0015</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7973±0.0011</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7719±0.0000</t>
+          <t>0.7228±0.0348</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.8047±0.0081</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,62 +1490,62 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.5664±0.0000</t>
+          <t>0.7414±0.0885</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7905±0.0000</t>
+          <t>0.7241±0.0507</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.5804±0.0000</t>
+          <t>0.7551±0.0500</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.7768±0.0000</t>
+          <t>0.7812±0.0507</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.5994±0.0000</t>
+          <t>0.6822±0.0875</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.5501±0.0000</t>
+          <t>0.8170±0.0150</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.5868±0.0000</t>
+          <t>0.6745±0.0984</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.5868±0.0000</t>
+          <t>0.6745±0.0984</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.5868±0.0000</t>
+          <t>0.6745±0.0984</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.5875±0.0000</t>
+          <t>0.8188±0.0150</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.7298±0.0000</t>
+          <t>0.5808±0.0155</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6350±0.0000</t>
+          <t>0.7031±0.0578</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1555,62 +1555,62 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.7927±0.0000</t>
+          <t>0.7439±0.0234</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.7603±0.0000</t>
+          <t>0.7881±0.0271</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.7842±0.0000</t>
+          <t>0.7348±0.0023</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.8113±0.0060</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.7807±0.0000</t>
+          <t>0.7938±0.0233</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.7495±0.0092</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.7950±0.0000</t>
+          <t>0.7923±0.0068</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.7950±0.0000</t>
+          <t>0.7923±0.0068</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.7950±0.0000</t>
+          <t>0.7923±0.0068</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.7896±0.0000</t>
+          <t>0.7849±0.0162</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.7464±0.0000</t>
+          <t>0.7312±0.0035</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.7980±0.0000</t>
+          <t>0.8010±0.0084</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7805±0.0000</t>
+          <t>0.7825±0.0232</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.7807±0.0000</t>
+          <t>0.7344±0.0133</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.7383±0.0000</t>
+          <t>0.7227±0.0125</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.7706±0.0000</t>
+          <t>0.7504±0.0040</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7759±0.0000</t>
+          <t>0.7822±0.0144</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7772±0.0000</t>
+          <t>0.7839±0.0289</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7717±0.0000</t>
+          <t>0.7788±0.0214</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7717±0.0000</t>
+          <t>0.7788±0.0214</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7717±0.0000</t>
+          <t>0.7788±0.0214</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7781±0.0000</t>
+          <t>0.7763±0.0244</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7990±0.0000</t>
+          <t>0.7672±0.0332</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7865±0.0000</t>
+          <t>0.7803±0.0136</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,62 +1685,62 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7965±0.0000</t>
+          <t>0.7939±0.0035</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7978±0.0000</t>
+          <t>0.7287±0.0060</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7347±0.0000</t>
+          <t>0.7278±0.0152</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7683±0.0000</t>
+          <t>0.7558±0.0248</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7869±0.0000</t>
+          <t>0.7815±0.0206</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7912±0.0000</t>
+          <t>0.7463±0.0093</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7931±0.0000</t>
+          <t>0.7460±0.0073</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7931±0.0000</t>
+          <t>0.7460±0.0073</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7931±0.0000</t>
+          <t>0.7460±0.0073</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7913±0.0000</t>
+          <t>0.7645±0.0106</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.8020±0.0000</t>
+          <t>0.7537±0.0333</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7879±0.0000</t>
+          <t>0.7751±0.0121</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.7799±0.0000</t>
+          <t>0.7473±0.0170</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.7940±0.0000</t>
+          <t>0.7995±0.0078</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.7163±0.0000</t>
+          <t>0.7292±0.0103</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7948±0.0000</t>
+          <t>0.8075±0.0097</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7561±0.0000</t>
+          <t>0.7474±0.0161</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7824±0.0000</t>
+          <t>0.7600±0.0233</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.7704±0.0000</t>
+          <t>0.7576±0.0262</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.7704±0.0000</t>
+          <t>0.7744±0.0228</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.7704±0.0000</t>
+          <t>0.7744±0.0228</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.7672±0.0000</t>
+          <t>0.7788±0.0193</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7011±0.0000</t>
+          <t>0.7301±0.0040</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.7809±0.0000</t>
+          <t>0.7573±0.0288</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7846±0.0000</t>
+          <t>0.7575±0.0352</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5304±0.0000</t>
+          <t>0.5867±0.0158</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3476±0.0000</t>
+          <t>0.4452±0.0789</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6393±0.0000</t>
+          <t>0.6194±0.0885</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.5207±0.0000</t>
+          <t>0.6314±0.0318</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5414±0.0000</t>
+          <t>0.6035±0.0222</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5321±0.0000</t>
+          <t>0.5757±0.0243</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.5820±0.0436</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.5820±0.0436</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.5820±0.0436</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5421±0.0000</t>
+          <t>0.6114±0.0265</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6263±0.0000</t>
+          <t>0.6341±0.0237</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5622±0.0000</t>
+          <t>0.6378±0.0232</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.7717±0.0347</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.6067±0.0000</t>
+          <t>0.6231±0.0224</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4840±0.0000</t>
+          <t>0.5214±0.0375</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6741±0.0000</t>
+          <t>0.6772±0.0135</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5945±0.0195</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6205±0.0000</t>
+          <t>0.6290±0.0186</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.6267±0.0000</t>
+          <t>0.6146±0.0197</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6365±0.0130</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6365±0.0130</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6365±0.0130</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.6358±0.0000</t>
+          <t>0.6125±0.0232</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6203±0.0000</t>
+          <t>0.6537±0.0100</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6154±0.0000</t>
+          <t>0.6396±0.0262</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7145±0.0318</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.4627±0.0000</t>
+          <t>0.5810±0.0778</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.3126±0.0000</t>
+          <t>0.4884±0.0680</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.4269±0.0000</t>
+          <t>0.5925±0.0205</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.4620±0.0000</t>
+          <t>0.5779±0.0599</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5498±0.0699</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.4524±0.0000</t>
+          <t>0.6182±0.0235</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.4479±0.0000</t>
+          <t>0.5072±0.0492</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.4479±0.0000</t>
+          <t>0.5072±0.0492</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.4479±0.0000</t>
+          <t>0.5072±0.0492</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.4893±0.0000</t>
+          <t>0.6077±0.0410</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.4871±0.0000</t>
+          <t>0.5214±0.0138</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.4932±0.0000</t>
+          <t>0.5351±0.0352</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.7931±0.0000</t>
+          <t>0.7252±0.0258</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.6501±0.0000</t>
+          <t>0.6109±0.0413</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4651±0.0000</t>
+          <t>0.6170±0.0293</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5914±0.0000</t>
+          <t>0.6351±0.0062</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6291±0.0105</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6144±0.0000</t>
+          <t>0.6323±0.0366</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.5770±0.0000</t>
+          <t>0.5843±0.0337</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6261±0.0000</t>
+          <t>0.6077±0.0132</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6261±0.0000</t>
+          <t>0.6077±0.0132</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6261±0.0000</t>
+          <t>0.6077±0.0132</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.5591±0.0000</t>
+          <t>0.6091±0.0393</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.6032±0.0000</t>
+          <t>0.6525±0.0158</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.6338±0.0000</t>
+          <t>0.6374±0.0305</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.7496±0.0000</t>
+          <t>0.7703±0.0427</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5999±0.0000</t>
+          <t>0.6307±0.0109</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2100±0.0000</t>
+          <t>0.4949±0.1527</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.5636±0.0000</t>
+          <t>0.6172±0.0159</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.5889±0.0000</t>
+          <t>0.6063±0.0110</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.5959±0.0000</t>
+          <t>0.6154±0.0096</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6083±0.0000</t>
+          <t>0.6435±0.0242</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6310±0.0083</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6310±0.0083</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6310±0.0083</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6035±0.0000</t>
+          <t>0.6288±0.0097</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.5899±0.0000</t>
+          <t>0.6350±0.0180</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6088±0.0000</t>
+          <t>0.6438±0.0108</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7503±0.0000</t>
+          <t>0.7701±0.0382</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.5888±0.0000</t>
+          <t>0.6125±0.0044</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.2273±0.0000</t>
+          <t>0.4725±0.1330</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5576±0.0000</t>
+          <t>0.6124±0.0343</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.5686±0.0000</t>
+          <t>0.6083±0.0105</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.5897±0.0000</t>
+          <t>0.6204±0.0193</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5898±0.0000</t>
+          <t>0.6312±0.0182</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5981±0.0000</t>
+          <t>0.6153±0.0093</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5981±0.0000</t>
+          <t>0.6153±0.0093</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5981±0.0000</t>
+          <t>0.6153±0.0093</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5887±0.0000</t>
+          <t>0.6540±0.0122</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.6250±0.0029</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6106±0.0000</t>
+          <t>0.6269±0.0096</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7690±0.0000</t>
+          <t>0.7792±0.0145</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5792±0.0000</t>
+          <t>0.5777±0.0092</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4946±0.0000</t>
+          <t>0.5739±0.0602</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5808±0.0000</t>
+          <t>0.6189±0.0162</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.4973±0.0000</t>
+          <t>0.5906±0.0651</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5576±0.0000</t>
+          <t>0.6006±0.0014</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5848±0.0000</t>
+          <t>0.5535±0.0177</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5655±0.0000</t>
+          <t>0.6071±0.0025</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5655±0.0000</t>
+          <t>0.6066±0.0191</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5655±0.0000</t>
+          <t>0.6066±0.0191</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.4952±0.0000</t>
+          <t>0.5550±0.0105</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.5763±0.0000</t>
+          <t>0.6178±0.0113</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6225±0.0000</t>
+          <t>0.6102±0.0108</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8604±0.0000</t>
+          <t>0.8369±0.0201</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6518±0.0000</t>
+          <t>0.7131±0.0107</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5599±0.0000</t>
+          <t>0.6391±0.0669</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7538±0.0000</t>
+          <t>0.7303±0.0705</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6344±0.0000</t>
+          <t>0.7421±0.0201</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6558±0.0000</t>
+          <t>0.7179±0.0228</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6529±0.0000</t>
+          <t>0.7055±0.0127</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6472±0.0000</t>
+          <t>0.7025±0.0434</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6472±0.0000</t>
+          <t>0.7025±0.0434</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6472±0.0000</t>
+          <t>0.7025±0.0434</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6555±0.0000</t>
+          <t>0.7268±0.0196</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7261±0.0000</t>
+          <t>0.7371±0.0169</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6773±0.0000</t>
+          <t>0.7372±0.0209</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8222±0.0000</t>
+          <t>0.8537±0.0249</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.6975±0.0000</t>
+          <t>0.7287±0.0069</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6583±0.0000</t>
+          <t>0.6712±0.0118</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7906±0.0000</t>
+          <t>0.7911±0.0225</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6998±0.0318</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7345±0.0000</t>
+          <t>0.7154±0.0220</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7165±0.0000</t>
+          <t>0.7282±0.0350</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6947±0.0000</t>
+          <t>0.7395±0.0203</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6947±0.0000</t>
+          <t>0.7396±0.0203</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6947±0.0000</t>
+          <t>0.7396±0.0203</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7303±0.0000</t>
+          <t>0.7218±0.0158</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7299±0.0000</t>
+          <t>0.7630±0.0027</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7023±0.0000</t>
+          <t>0.7337±0.0350</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.8325±0.0000</t>
+          <t>0.8032±0.0351</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6482±0.0000</t>
+          <t>0.6997±0.0481</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5717±0.0000</t>
+          <t>0.6514±0.0487</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6214±0.0000</t>
+          <t>0.7018±0.0196</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6536±0.0000</t>
+          <t>0.6856±0.0422</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6612±0.0000</t>
+          <t>0.6716±0.0420</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6305±0.0000</t>
+          <t>0.7137±0.0146</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6315±0.0000</t>
+          <t>0.6473±0.0129</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6314±0.0000</t>
+          <t>0.6473±0.0129</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6315±0.0000</t>
+          <t>0.6473±0.0129</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6550±0.0000</t>
+          <t>0.7217±0.0242</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.6892±0.0000</t>
+          <t>0.7128±0.0077</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.6544±0.0116</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.8786±0.0000</t>
+          <t>0.8235±0.0285</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7520±0.0000</t>
+          <t>0.7294±0.0382</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6502±0.0000</t>
+          <t>0.7384±0.0293</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.7451±0.0109</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7330±0.0103</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7306±0.0000</t>
+          <t>0.7351±0.0206</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6986±0.0000</t>
+          <t>0.7073±0.0253</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7379±0.0000</t>
+          <t>0.7280±0.0144</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7379±0.0000</t>
+          <t>0.7280±0.0144</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7379±0.0000</t>
+          <t>0.7280±0.0144</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6614±0.0000</t>
+          <t>0.7241±0.0349</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7153±0.0000</t>
+          <t>0.7531±0.0099</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7424±0.0000</t>
+          <t>0.7447±0.0233</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.8449±0.0000</t>
+          <t>0.8518±0.0235</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7296±0.0000</t>
+          <t>0.7309±0.0235</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5019±0.0000</t>
+          <t>0.6578±0.0931</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7029±0.0000</t>
+          <t>0.7353±0.0063</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7279±0.0000</t>
+          <t>0.7347±0.0160</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7323±0.0000</t>
+          <t>0.7414±0.0131</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7383±0.0000</t>
+          <t>0.7518±0.0154</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7528±0.0056</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7525±0.0057</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7526±0.0054</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7277±0.0000</t>
+          <t>0.7436±0.0098</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7013±0.0000</t>
+          <t>0.7398±0.0174</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7016±0.0000</t>
+          <t>0.7460±0.0213</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.8465±0.0000</t>
+          <t>0.8519±0.0227</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7182±0.0000</t>
+          <t>0.7360±0.0018</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5074±0.0000</t>
+          <t>0.6397±0.0788</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7040±0.0000</t>
+          <t>0.7481±0.0235</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.7365±0.0163</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7124±0.0000</t>
+          <t>0.7410±0.0213</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7062±0.0000</t>
+          <t>0.7519±0.0172</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7296±0.0000</t>
+          <t>0.7399±0.0138</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7300±0.0000</t>
+          <t>0.7405±0.0136</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7300±0.0000</t>
+          <t>0.7405±0.0136</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7641±0.0215</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7039±0.0000</t>
+          <t>0.7310±0.0047</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7041±0.0000</t>
+          <t>0.7214±0.0172</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.8670±0.0000</t>
+          <t>0.8668±0.0121</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7074±0.0000</t>
+          <t>0.7254±0.0021</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6631±0.0000</t>
+          <t>0.7029±0.0311</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7026±0.0000</t>
+          <t>0.7240±0.0090</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7150±0.0363</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6917±0.0000</t>
+          <t>0.7131±0.0017</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7121±0.0000</t>
+          <t>0.6967±0.0190</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6951±0.0000</t>
+          <t>0.7163±0.0014</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6951±0.0000</t>
+          <t>0.7172±0.0110</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6951±0.0000</t>
+          <t>0.7172±0.0110</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.6464±0.0000</t>
+          <t>0.6935±0.0180</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7075±0.0000</t>
+          <t>0.7443±0.0087</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7271±0.0000</t>
+          <t>0.7175±0.0061</t>
         </is>
       </c>
     </row>
